--- a/data/sce_compartment_curation/2026_curated/lipid_droplet_annotations.xlsx
+++ b/data/sce_compartment_curation/2026_curated/lipid_droplet_annotations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,16 +1716,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TLD1</t>
+          <t>CAB5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YDR275W</t>
+          <t>YDR196C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1751,7 +1751,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1766,27 +1766,27 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ERG1</t>
+          <t>TLD1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YGR175C</t>
+          <t>YDR275W</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1812,7 +1812,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1827,18 +1827,18 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Leber R, et al. (1998) PMID:9450962</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1888,27 +1888,27 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Leber R, et al. (1998) PMID:9450962</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAY1</t>
+          <t>ERG1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YGR263C</t>
+          <t>YGR175C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1960,16 +1960,16 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NEM1</t>
+          <t>SAY1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YHR004C</t>
+          <t>YGR263C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2010,27 +2010,27 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2016-01-13</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Wolinski H, et al. (2015) PMID:26275961</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ERG7</t>
+          <t>NEM1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YHR072W</t>
+          <t>YHR004C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2071,18 +2071,18 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2016-01-13</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Wolinski H, et al. (2015) PMID:26275961</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2132,18 +2132,18 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2193,27 +2193,27 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Milla P, et al. (2002) PMID:11706015</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AYR1</t>
+          <t>ERG7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YIL124W</t>
+          <t>YHR072W</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2254,18 +2254,18 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Milla P, et al. (2002) PMID:11706015</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2315,27 +2315,27 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Athenstaedt K and Daum G (2000) PMID:10617610</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ANR2</t>
+          <t>AYR1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YKL047W</t>
+          <t>YIL124W</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2376,27 +2376,27 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Athenstaedt K and Daum G (2000) PMID:10617610</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YJU3</t>
+          <t>ANR2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YKL094W</t>
+          <t>YKL047W</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2437,18 +2437,18 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Heier C, et al. (2010) PMID:20554061</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2559,27 +2559,27 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Heier C, et al. (2010) PMID:20554061</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TGL1</t>
+          <t>YJU3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YKL140W</t>
+          <t>YKL094W</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2620,18 +2620,18 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Köffel R, et al. (2005) PMID:15713625</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2686,13 +2686,13 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Köffel R, et al. (2005) PMID:15713625</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2742,27 +2742,27 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FAS1</t>
+          <t>TGL1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YKL182W</t>
+          <t>YKL140W</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2803,27 +2803,27 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Desfougères T, et al. (2008) PMID:17803462</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PLN1</t>
+          <t>FAS1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YKR046C</t>
+          <t>YKL182W</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2864,18 +2864,18 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Desfougères T, et al. (2008) PMID:17803462</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2925,27 +2925,27 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GPT2</t>
+          <t>PLN1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YKR067W</t>
+          <t>YKR046C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2991,13 +2991,13 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Marr N, et al. (2012) PMID:22267742</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3052,22 +3052,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Athenstaedt K and Daum G (1997) PMID:9401016</t>
+          <t>Marr N, et al. (2012) PMID:22267742</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TGL4</t>
+          <t>GPT2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YKR089C</t>
+          <t>YKR067W</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3113,13 +3113,13 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Kurat CF, et al. (2006) PMID:16267052</t>
+          <t>Athenstaedt K and Daum G (1997) PMID:9401016</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3169,18 +3169,18 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Kurat CF, et al. (2006) PMID:16267052</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3291,18 +3291,18 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Athenstaedt K and Daum G (2005) PMID:16135509</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3352,27 +3352,27 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Lam C, et al. (2014) PMID:24390141</t>
+          <t>Athenstaedt K and Daum G (2005) PMID:16135509</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YEH1</t>
+          <t>TGL4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YLL012W</t>
+          <t>YKR089C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3398,7 +3398,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3413,18 +3413,18 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Köffel R, et al. (2005) PMID:15713625</t>
+          <t>Lam C, et al. (2014) PMID:24390141</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3474,27 +3474,27 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Köffel R, et al. (2005) PMID:15713625</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ERG27</t>
+          <t>YEH1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YLR100W</t>
+          <t>YLL012W</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3520,7 +3520,7 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3535,27 +3535,27 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CSR1</t>
+          <t>ERG27</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YLR380W</t>
+          <t>YLR100W</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3596,27 +3596,27 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Desfougères T, et al. (2008) PMID:17803462</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ERG6</t>
+          <t>CSR1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YML008C</t>
+          <t>YLR380W</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3657,18 +3657,18 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Desfougères T, et al. (2008) PMID:17803462</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3718,27 +3718,27 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UBX2</t>
+          <t>ERG6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YML013W</t>
+          <t>YML008C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3779,18 +3779,18 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3840,27 +3840,27 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Wang CW and Lee SC (2012) PMID:22454508</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SRT1</t>
+          <t>UBX2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YMR101C</t>
+          <t>YML013W</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3886,7 +3886,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3901,18 +3901,18 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Lam C, et al. (2014) PMID:24390141</t>
+          <t>Wang CW and Lee SC (2012) PMID:22454508</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3962,27 +3962,27 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sato M, et al. (2001) PMID:11442630</t>
+          <t>Lam C, et al. (2014) PMID:24390141</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HFD1</t>
+          <t>SRT1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YMR110C</t>
+          <t>YMR101C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4023,18 +4023,18 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Sato M, et al. (2001) PMID:11442630</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4084,27 +4084,27 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YIM1</t>
+          <t>HFD1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YMR152W</t>
+          <t>YMR110C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4130,7 +4130,7 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4145,18 +4145,18 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -4206,27 +4206,27 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PAH1</t>
+          <t>YIM1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YMR165C</t>
+          <t>YMR152W</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4267,27 +4267,27 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2016-01-13</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Wolinski H, et al. (2015) PMID:26275961</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FAA4</t>
+          <t>PAH1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YMR246W</t>
+          <t>YMR165C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4328,18 +4328,18 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2016-01-13</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Adhikari S, et al. (2021) PMID:34161133</t>
+          <t>Wolinski H, et al. (2015) PMID:26275961</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4389,18 +4389,18 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Adhikari S, et al. (2021) PMID:34161133</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4450,27 +4450,27 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TGL3</t>
+          <t>FAA4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YMR313C</t>
+          <t>YMR246W</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4522,7 +4522,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4572,18 +4572,18 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4633,18 +4633,18 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Lam C, et al. (2014) PMID:24390141</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4694,27 +4694,27 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Kurat CF, et al. (2006) PMID:16267052</t>
+          <t>Lam C, et al. (2014) PMID:24390141</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PDR16</t>
+          <t>TGL3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YNL231C</t>
+          <t>YMR313C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4755,18 +4755,18 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2014-01-25</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ren J, et al. (2014) PMID:24403601</t>
+          <t>Kurat CF, et al. (2006) PMID:16267052</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4816,27 +4816,27 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-01-25</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Schnabl M, et al. (2003) PMID:12869188</t>
+          <t>Ren J, et al. (2014) PMID:24403601</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LRO1</t>
+          <t>PDR16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YNR008W</t>
+          <t>YNL231C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4882,22 +4882,22 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Wang CW and Lee SC (2012) PMID:22454508</t>
+          <t>Schnabl M, et al. (2003) PMID:12869188</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LDS2</t>
+          <t>LRO1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>YOL047C</t>
+          <t>YNR008W</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4923,7 +4923,7 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4938,27 +4938,27 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Lam C, et al. (2014) PMID:24390141</t>
+          <t>Wang CW and Lee SC (2012) PMID:22454508</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RRT8</t>
+          <t>LDS2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>YOL048C</t>
+          <t>YOL047C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Lam C, et al. (2014) PMID:24390141</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LPL1</t>
+          <t>RRT8</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YOR059C</t>
+          <t>YOL048C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5045,7 +5045,7 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5060,18 +5060,18 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5121,18 +5121,18 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -5182,27 +5182,27 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2014-07-26</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Selvaraju K, et al. (2014) PMID:25014274</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TGL5</t>
+          <t>LPL1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YOR081C</t>
+          <t>YOR059C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5243,18 +5243,18 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2014-07-26</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Selvaraju K, et al. (2014) PMID:25014274</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -5304,18 +5304,18 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Athenstaedt K and Daum G (2005) PMID:16135509</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5365,27 +5365,27 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Athenstaedt K and Daum G (2005) PMID:16135509</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DGA1</t>
+          <t>TGL5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>YOR245C</t>
+          <t>YOR081C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5411,7 +5411,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5426,18 +5426,18 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Sorger D and Daum G (2002) PMID:11751830</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5487,27 +5487,27 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Sorger D and Daum G (2002) PMID:11751830</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ENV9</t>
+          <t>DGA1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>YOR246C</t>
+          <t>YOR245C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5533,7 +5533,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5548,27 +5548,27 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SPS4</t>
+          <t>ENV9</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>YOR313C</t>
+          <t>YOR246C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5614,22 +5614,22 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Lam C, et al. (2014) PMID:24390141</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FAA1</t>
+          <t>SPS4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>YOR317W</t>
+          <t>YOR313C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5655,7 +5655,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5670,18 +5670,18 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Lam C, et al. (2014) PMID:24390141</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5731,27 +5731,27 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ATF1</t>
+          <t>FAA1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>YOR377W</t>
+          <t>YOR317W</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Verstrepen KJ, et al. (2004) PMID:15042596</t>
+          <t>Athenstaedt K, et al. (1999) PMID:10515935</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PGC1</t>
+          <t>ATF1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YPL206C</t>
+          <t>YOR377W</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5858,13 +5858,13 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Beilharz T, et al. (2003) PMID:12514182</t>
+          <t>Verstrepen KJ, et al. (2004) PMID:15042596</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5914,27 +5914,27 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Currie E, et al. (2014) PMID:24868093</t>
+          <t>Beilharz T, et al. (2003) PMID:12514182</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LOA1</t>
+          <t>PGC1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YPR139C</t>
+          <t>YPL206C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5975,18 +5975,18 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Grillitsch K, et al. (2011) PMID:21820081</t>
+          <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -6041,22 +6041,22 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Ayciriex S, et al. (2012) PMID:22090344</t>
+          <t>Grillitsch K, et al. (2011) PMID:21820081</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YPR147C</t>
+          <t>LOA1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YPR147C</t>
+          <t>YPR139C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6097,10 +6097,71 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
+          <t>2013-08-07</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Ayciriex S, et al. (2012) PMID:22090344</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>YPR147C</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>YPR147C</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>located in</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>GO:0005811</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>lipid droplet</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>cellular component</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>manually curated</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
           <t>2014-06-06</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Currie E, et al. (2014) PMID:24868093</t>
         </is>
